--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOUTH259\My Briefcase\GitHub\KM-Election\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\KM-Election\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -7463,7 +7463,7 @@
         <v>8</v>
       </c>
       <c r="F279" s="3" t="str">
-        <f t="shared" ref="F279:F280" si="39">B279&amp;".jpg"</f>
+        <f t="shared" ref="F279:F281" si="39">B279&amp;".jpg"</f>
         <v>蔡建偉2.jpg</v>
       </c>
     </row>
@@ -7504,7 +7504,10 @@
       <c r="E281" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F281" s="3"/>
+      <c r="F281" s="9" t="str">
+        <f t="shared" si="39"/>
+        <v>蔡是民.jpg</v>
+      </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="3">
